--- a/results/train/binary_AD_results.xlsx
+++ b/results/train/binary_AD_results.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,70 +455,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -531,54 +496,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.785</v>
+        <v>0.77441</v>
       </c>
       <c r="C2" t="n">
-        <v>0.725</v>
+        <v>0.69829</v>
       </c>
       <c r="D2" t="n">
-        <v>0.855</v>
+        <v>0.86916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.88462</v>
       </c>
       <c r="I2" t="n">
-        <v>0.84</v>
+        <v>0.33333</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="R2" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -589,54 +533,33 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.781</v>
+        <v>0.77239</v>
       </c>
       <c r="C3" t="n">
-        <v>0.712</v>
+        <v>0.695</v>
       </c>
       <c r="D3" t="n">
-        <v>0.865</v>
+        <v>0.86916</v>
       </c>
       <c r="E3" t="n">
-        <v>0.832</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.832</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.84615</v>
       </c>
       <c r="I3" t="n">
-        <v>0.832</v>
+        <v>0.33333</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="R3" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -647,54 +570,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.799</v>
+        <v>0.769</v>
       </c>
       <c r="C4" t="n">
-        <v>0.739</v>
+        <v>0.68377</v>
       </c>
       <c r="D4" t="n">
-        <v>0.87</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.88462</v>
       </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>0.33333</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.744</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="R4" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -705,54 +607,33 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.787</v>
+        <v>0.76727</v>
       </c>
       <c r="C5" t="n">
-        <v>0.722</v>
+        <v>0.68676</v>
       </c>
       <c r="D5" t="n">
-        <v>0.865</v>
+        <v>0.86916</v>
       </c>
       <c r="E5" t="n">
-        <v>0.839</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.839</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.84615</v>
       </c>
       <c r="I5" t="n">
-        <v>0.839</v>
+        <v>0.33333</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="R5" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -767,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,70 +674,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -869,55 +715,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.755</v>
+        <v>0.74683</v>
       </c>
       <c r="C2" t="n">
-        <v>0.725</v>
+        <v>0.69829</v>
       </c>
       <c r="D2" t="n">
-        <v>0.788</v>
+        <v>0.80262</v>
       </c>
       <c r="E2" t="n">
-        <v>0.825</v>
+        <v>0.9603</v>
       </c>
       <c r="F2" t="n">
-        <v>0.958</v>
+        <v>0.9819</v>
       </c>
       <c r="G2" t="n">
-        <v>0.834</v>
+        <v>0.93715</v>
       </c>
       <c r="H2" t="n">
-        <v>0.982</v>
+        <v>0.8343699999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.22778</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.50437</v>
       </c>
       <c r="K2" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.828</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.738</v>
+        <v>0.73761</v>
       </c>
     </row>
     <row r="3">
@@ -927,55 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.744</v>
+        <v>0.73947</v>
       </c>
       <c r="C3" t="n">
-        <v>0.712</v>
+        <v>0.695</v>
       </c>
       <c r="D3" t="n">
-        <v>0.78</v>
+        <v>0.79001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.95806</v>
       </c>
       <c r="F3" t="n">
-        <v>0.956</v>
+        <v>0.97143</v>
       </c>
       <c r="G3" t="n">
-        <v>0.822</v>
+        <v>0.93773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.971</v>
+        <v>0.79332</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.20556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.51372</v>
       </c>
       <c r="K3" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.733</v>
+        <v>0.73297</v>
       </c>
     </row>
     <row r="4">
@@ -985,55 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.764</v>
+        <v>0.73922</v>
       </c>
       <c r="C4" t="n">
-        <v>0.739</v>
+        <v>0.68377</v>
       </c>
       <c r="D4" t="n">
-        <v>0.792</v>
+        <v>0.80447</v>
       </c>
       <c r="E4" t="n">
-        <v>0.834</v>
+        <v>0.96</v>
       </c>
       <c r="F4" t="n">
-        <v>0.958</v>
+        <v>0.98149</v>
       </c>
       <c r="G4" t="n">
-        <v>0.843</v>
+        <v>0.9333900000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.981</v>
+        <v>0.82852</v>
       </c>
       <c r="I4" t="n">
-        <v>0.825</v>
+        <v>0.22778</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.59726</v>
       </c>
       <c r="K4" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.803</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.712</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.68692</v>
       </c>
     </row>
     <row r="5">
@@ -1043,55 +826,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.746</v>
+        <v>0.73398</v>
       </c>
       <c r="C5" t="n">
-        <v>0.722</v>
+        <v>0.68676</v>
       </c>
       <c r="D5" t="n">
-        <v>0.771</v>
+        <v>0.78818</v>
       </c>
       <c r="E5" t="n">
-        <v>0.823</v>
+        <v>0.95806</v>
       </c>
       <c r="F5" t="n">
-        <v>0.956</v>
+        <v>0.91567</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.94095</v>
       </c>
       <c r="H5" t="n">
-        <v>0.916</v>
+        <v>0.7883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.20556</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.5775400000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.748</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.697</v>
+        <v>0.69651</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,70 +893,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1207,55 +934,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.711</v>
+        <v>0.71331</v>
       </c>
       <c r="C2" t="n">
-        <v>0.725</v>
+        <v>0.69829</v>
       </c>
       <c r="D2" t="n">
-        <v>0.698</v>
+        <v>0.72899</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.9257</v>
       </c>
       <c r="F2" t="n">
-        <v>0.917</v>
+        <v>0.89289</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8</v>
+        <v>0.8186600000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.893</v>
+        <v>0.77251</v>
       </c>
       <c r="I2" t="n">
-        <v>0.769</v>
+        <v>0.17302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.819</v>
+        <v>0.37504</v>
       </c>
       <c r="K2" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.641</v>
+        <v>0.64149</v>
       </c>
     </row>
     <row r="3">
@@ -1265,55 +971,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.696</v>
+        <v>0.7003</v>
       </c>
       <c r="C3" t="n">
-        <v>0.712</v>
+        <v>0.695</v>
       </c>
       <c r="D3" t="n">
-        <v>0.681</v>
+        <v>0.70567</v>
       </c>
       <c r="E3" t="n">
-        <v>0.796</v>
+        <v>0.90837</v>
       </c>
       <c r="F3" t="n">
-        <v>0.903</v>
+        <v>0.8696199999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.783</v>
+        <v>0.79518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.87</v>
+        <v>0.72536</v>
       </c>
       <c r="I3" t="n">
-        <v>0.751</v>
+        <v>0.15635</v>
       </c>
       <c r="J3" t="n">
-        <v>0.795</v>
+        <v>0.37803</v>
       </c>
       <c r="K3" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.631</v>
+        <v>0.6307</v>
       </c>
     </row>
     <row r="4">
@@ -1323,55 +1008,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.733</v>
+        <v>0.71502</v>
       </c>
       <c r="C4" t="n">
-        <v>0.739</v>
+        <v>0.68377</v>
       </c>
       <c r="D4" t="n">
-        <v>0.728</v>
+        <v>0.74927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.822</v>
+        <v>0.93132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.926</v>
+        <v>0.91706</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.86243</v>
       </c>
       <c r="H4" t="n">
-        <v>0.917</v>
+        <v>0.77378</v>
       </c>
       <c r="I4" t="n">
-        <v>0.796</v>
+        <v>0.19222</v>
       </c>
       <c r="J4" t="n">
-        <v>0.862</v>
+        <v>0.46544</v>
       </c>
       <c r="K4" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.644</v>
+        <v>0.64425</v>
       </c>
     </row>
     <row r="5">
@@ -1381,54 +1045,33 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.71</v>
+        <v>0.7037600000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.722</v>
+        <v>0.68676</v>
       </c>
       <c r="D5" t="n">
-        <v>0.698</v>
+        <v>0.72163</v>
       </c>
       <c r="E5" t="n">
-        <v>0.803</v>
+        <v>0.90837</v>
       </c>
       <c r="F5" t="n">
-        <v>0.903</v>
+        <v>0.85405</v>
       </c>
       <c r="G5" t="n">
-        <v>0.783</v>
+        <v>0.85843</v>
       </c>
       <c r="H5" t="n">
-        <v>0.854</v>
+        <v>0.72704</v>
       </c>
       <c r="I5" t="n">
-        <v>0.784</v>
+        <v>0.16111</v>
       </c>
       <c r="J5" t="n">
-        <v>0.858</v>
+        <v>0.43857</v>
       </c>
       <c r="K5" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="R5" t="n">
         <v>0.642</v>
       </c>
     </row>
@@ -1443,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,70 +1112,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1545,55 +1153,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.633</v>
+        <v>0.6681</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.67428</v>
       </c>
       <c r="D2" t="n">
-        <v>0.59</v>
+        <v>0.6620200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.766</v>
+        <v>0.89771</v>
       </c>
       <c r="F2" t="n">
-        <v>0.871</v>
+        <v>0.679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.681</v>
+        <v>0.69658</v>
       </c>
       <c r="H2" t="n">
-        <v>0.679</v>
+        <v>0.761</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.13889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.697</v>
+        <v>0.31977</v>
       </c>
       <c r="K2" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.467</v>
+        <v>0.4671</v>
       </c>
     </row>
     <row r="3">
@@ -1603,55 +1190,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.621</v>
+        <v>0.65527</v>
       </c>
       <c r="C3" t="n">
-        <v>0.669</v>
+        <v>0.66866</v>
       </c>
       <c r="D3" t="n">
-        <v>0.58</v>
+        <v>0.64241</v>
       </c>
       <c r="E3" t="n">
-        <v>0.769</v>
+        <v>0.90837</v>
       </c>
       <c r="F3" t="n">
-        <v>0.903</v>
+        <v>0.66409</v>
       </c>
       <c r="G3" t="n">
-        <v>0.667</v>
+        <v>0.62177</v>
       </c>
       <c r="H3" t="n">
-        <v>0.664</v>
+        <v>0.7139</v>
       </c>
       <c r="I3" t="n">
-        <v>0.645</v>
+        <v>0.13889</v>
       </c>
       <c r="J3" t="n">
-        <v>0.622</v>
+        <v>0.325</v>
       </c>
       <c r="K3" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.474</v>
+        <v>0.47366</v>
       </c>
     </row>
     <row r="4">
@@ -1661,55 +1227,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.69063</v>
       </c>
       <c r="C4" t="n">
-        <v>0.705</v>
+        <v>0.66252</v>
       </c>
       <c r="D4" t="n">
-        <v>0.676</v>
+        <v>0.72124</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8</v>
+        <v>0.93132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.926</v>
+        <v>0.80833</v>
       </c>
       <c r="G4" t="n">
-        <v>0.753</v>
+        <v>0.81403</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.756</v>
+        <v>0.19222</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.41431</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6860000000000001</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.582</v>
+        <v>0.5822000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1719,55 +1264,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.667</v>
+        <v>0.6767</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.66636</v>
       </c>
       <c r="D5" t="n">
-        <v>0.646</v>
+        <v>0.68736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.782</v>
+        <v>0.90837</v>
       </c>
       <c r="F5" t="n">
-        <v>0.903</v>
+        <v>0.78103</v>
       </c>
       <c r="G5" t="n">
-        <v>0.732</v>
+        <v>0.75593</v>
       </c>
       <c r="H5" t="n">
-        <v>0.781</v>
+        <v>0.7139</v>
       </c>
       <c r="I5" t="n">
-        <v>0.721</v>
+        <v>0.16111</v>
       </c>
       <c r="J5" t="n">
-        <v>0.756</v>
+        <v>0.38615</v>
       </c>
       <c r="K5" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.577</v>
+        <v>0.5769300000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,70 +1331,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1883,55 +1372,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.746</v>
+        <v>0.7432800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.72</v>
+        <v>0.69589</v>
       </c>
       <c r="D2" t="n">
-        <v>0.777</v>
+        <v>0.80045</v>
       </c>
       <c r="E2" t="n">
-        <v>0.822</v>
+        <v>0.963</v>
       </c>
       <c r="F2" t="n">
-        <v>0.958</v>
+        <v>0.9410500000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.91453</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.8347599999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.804</v>
+        <v>0.25016</v>
       </c>
       <c r="J2" t="n">
-        <v>0.915</v>
+        <v>0.5383</v>
       </c>
       <c r="K2" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.716</v>
+        <v>0.71629</v>
       </c>
     </row>
     <row r="3">
@@ -1941,55 +1409,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.737</v>
+        <v>0.73638</v>
       </c>
       <c r="C3" t="n">
-        <v>0.708</v>
+        <v>0.69237</v>
       </c>
       <c r="D3" t="n">
-        <v>0.774</v>
+        <v>0.79004</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.9599299999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.958</v>
+        <v>0.93176</v>
       </c>
       <c r="G3" t="n">
-        <v>0.803</v>
+        <v>0.9025300000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.79292</v>
       </c>
       <c r="I3" t="n">
-        <v>0.79</v>
+        <v>0.24016</v>
       </c>
       <c r="J3" t="n">
-        <v>0.903</v>
+        <v>0.58222</v>
       </c>
       <c r="K3" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.713</v>
+        <v>0.71339</v>
       </c>
     </row>
     <row r="4">
@@ -1999,55 +1446,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.765</v>
+        <v>0.74143</v>
       </c>
       <c r="C4" t="n">
-        <v>0.736</v>
+        <v>0.68164</v>
       </c>
       <c r="D4" t="n">
-        <v>0.799</v>
+        <v>0.81472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.835</v>
+        <v>0.9674</v>
       </c>
       <c r="F4" t="n">
-        <v>0.965</v>
+        <v>0.95869</v>
       </c>
       <c r="G4" t="n">
-        <v>0.832</v>
+        <v>0.93391</v>
       </c>
       <c r="H4" t="n">
-        <v>0.959</v>
+        <v>0.83326</v>
       </c>
       <c r="I4" t="n">
-        <v>0.822</v>
+        <v>0.25933</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.6337</v>
       </c>
       <c r="K4" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.713</v>
+        <v>0.71315</v>
       </c>
     </row>
     <row r="5">
@@ -2057,55 +1483,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.747</v>
+        <v>0.73552</v>
       </c>
       <c r="C5" t="n">
-        <v>0.719</v>
+        <v>0.68472</v>
       </c>
       <c r="D5" t="n">
-        <v>0.781</v>
+        <v>0.79718</v>
       </c>
       <c r="E5" t="n">
-        <v>0.821</v>
+        <v>0.9599299999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.958</v>
+        <v>0.92361</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.9295600000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.924</v>
+        <v>0.79175</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.24333</v>
       </c>
       <c r="J5" t="n">
-        <v>0.93</v>
+        <v>0.61959</v>
       </c>
       <c r="K5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.715</v>
+        <v>0.71504</v>
       </c>
     </row>
   </sheetData>
